--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
@@ -97,10 +106,13 @@
     <t>MACARIO</t>
   </si>
   <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>NIEVES</t>
@@ -118,10 +130,13 @@
     <t>NERI</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
   </si>
   <si>
     <t>CANDIDO</t>
@@ -137,12 +152,6 @@
   </si>
   <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
   </si>
 </sst>
 </file>
@@ -686,16 +695,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>86.11</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -709,16 +721,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -732,16 +747,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -755,16 +773,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +850,7 @@
         <v>86.11</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -881,7 +902,7 @@
         <v>83.33</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -898,16 +919,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,22 +970,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920176</v>
+        <v>22330051920299</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -972,16 +993,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920069</v>
+        <v>21330051920167</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -995,62 +1016,62 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920426</v>
+        <v>21330051920169</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920314</v>
+        <v>21330051920176</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920166</v>
+        <v>20330051920069</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1059,27 +1080,27 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920167</v>
+        <v>22330051920426</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1087,24 +1108,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920169</v>
+        <v>22330051920314</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920166</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F9" t="s">
         <v>14</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
@@ -85,42 +85,42 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>VICENTE</t>
   </si>
   <si>
     <t>MACARIO</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>QUINTANA</t>
   </si>
   <si>
@@ -130,19 +130,19 @@
     <t>NERI</t>
   </si>
   <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
     <t>TONALLI</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
   </si>
   <si>
     <t>CRISTIAN</t>
@@ -970,7 +970,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920299</v>
+        <v>21330051920167</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -982,10 +982,10 @@
         <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920167</v>
+        <v>21330051920169</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920169</v>
+        <v>21330051920176</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920176</v>
+        <v>20330051920069</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920069</v>
+        <v>22330051920299</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1074,13 +1074,13 @@
         <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1111,7 +1111,7 @@
         <v>22330051920314</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -88,70 +88,10 @@
     <t>MAYO</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>QUINTANA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
     <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -841,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>86.11</v>
+        <v>94.44</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -867,16 +807,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -893,16 +833,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>96.67</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -919,13 +859,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H5">
         <v>8</v>
@@ -938,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -976,10 +916,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -988,167 +928,6 @@
         <v>14</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920169</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920176</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920069</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920299</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920426</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920314</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920166</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
@@ -790,7 +790,7 @@
         <v>94.44</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,7 +816,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -842,7 +842,7 @@
         <v>96.67</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,7 +868,7 @@
         <v>96</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20231.xlsx
@@ -790,7 +790,7 @@
         <v>94.44</v>
       </c>
       <c r="H2">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,7 +816,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -842,7 +842,7 @@
         <v>96.67</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,7 +868,7 @@
         <v>96</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
